--- a/GameData/DataTables/Meta/EventTable.xlsx
+++ b/GameData/DataTables/Meta/EventTable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,17 +445,62 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>EventType</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>EventKind</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MinStage</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>DayWeight</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NightWeight</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>TimeCost</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>RewardFee</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PlaceKey</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Repeatable</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>FailureWrapUp</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>RewardMaterialKey</t>
         </is>
       </c>
     </row>
@@ -477,12 +522,57 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -494,22 +584,358 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>事件模板的骨架定义</t>
+          <t>普通供给事件模板</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>事件稳定键</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>事件显示名称</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>事件类型（地图交互／调查／普通维修／怪谈阶段等）</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>EventKind 数值</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>最早投放阶段</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>白天投放权重</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>夜晚投放权重</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>完成后消耗的时间格</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>完成奖励维修费</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>投放地点稳定键</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>是否可重复</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>失败收尾文案</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>奖励材料稳定键，空表示无</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EV-N01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>卡住的卷帘门</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>40</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>本单失败结案</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>MT-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EV-N02</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>旧台灯接线</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>40</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>本单失败结案</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>MT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EV-N03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>货架后的隔板</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>本单失败结案</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>MT-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EV-D01</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>夜班送还</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>street</t>
+        </is>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>未交付仍记在订单里</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EV-D02</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>邻里帮忙找物</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>community</t>
+        </is>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>未找到可继续调查</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EV-I01</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>修复记录核对</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>可重新核对</t>
         </is>
       </c>
     </row>
